--- a/templates/R80302書式/計画申請/02_事業展開等実施計画(様式第1-3号)_企業名.xlsx
+++ b/templates/R80302書式/計画申請/02_事業展開等実施計画(様式第1-3号)_企業名.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="559" documentId="13_ncr:1_{221FBDEB-0959-4DCF-A894-D831578F3282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA7C972C-4AFC-4A51-86DB-0E15F3130F31}"/>
+  <xr:revisionPtr revIDLastSave="560" documentId="13_ncr:1_{221FBDEB-0959-4DCF-A894-D831578F3282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4267A0B-D51A-4214-80F3-3E79A05560CD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44040" yWindow="11220" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="様式第１－３号 " sheetId="5" r:id="rId1"/>
@@ -2242,7 +2242,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2325,19 +2325,13 @@
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -2347,10 +2341,10 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2375,244 +2369,236 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2640,7 +2626,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3195,7 +3181,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AY106"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.25" style="1" customWidth="1"/>
@@ -3216,8 +3202,8 @@
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:51" ht="18" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A1" s="36" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="12"/>
@@ -3237,7 +3223,7 @@
       <c r="P1" s="26"/>
       <c r="Q1" s="26"/>
     </row>
-    <row r="2" spans="1:51" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:51" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -3256,49 +3242,49 @@
       <c r="P2" s="12"/>
       <c r="Q2" s="12"/>
     </row>
-    <row r="3" spans="1:51" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="89" t="s">
+    <row r="3" spans="1:51" ht="24.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="89"/>
-    </row>
-    <row r="4" spans="1:51" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="90" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+    </row>
+    <row r="4" spans="1:51" ht="24.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A4" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="90"/>
-      <c r="O4" s="90"/>
-      <c r="P4" s="90"/>
-      <c r="Q4" s="90"/>
-    </row>
-    <row r="5" spans="1:51" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+    </row>
+    <row r="5" spans="1:51" ht="21" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A5" s="13" t="s">
         <v>2</v>
       </c>
@@ -3319,47 +3305,47 @@
       <c r="P5" s="12"/>
       <c r="Q5" s="12"/>
     </row>
-    <row r="6" spans="1:51" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="32"/>
-      <c r="B6" s="91" t="s">
+    <row r="6" spans="1:51" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A6" s="30"/>
+      <c r="B6" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="91"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="91"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="91"/>
-      <c r="L6" s="91"/>
-      <c r="M6" s="91"/>
-      <c r="N6" s="91"/>
-      <c r="O6" s="91"/>
-      <c r="P6" s="91"/>
-      <c r="Q6" s="91"/>
-    </row>
-    <row r="7" spans="1:51" s="4" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="93" t="s">
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+    </row>
+    <row r="7" spans="1:51" s="4" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A7" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="94"/>
-      <c r="P7" s="97"/>
-      <c r="Q7" s="98"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="65"/>
+      <c r="Q7" s="66"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
@@ -3393,26 +3379,26 @@
       <c r="AX7" s="9"/>
       <c r="AY7" s="10"/>
     </row>
-    <row r="8" spans="1:51" s="4" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="95" t="s">
+    <row r="8" spans="1:51" s="4" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A8" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
-      <c r="N8" s="96"/>
-      <c r="O8" s="96"/>
-      <c r="P8" s="99"/>
-      <c r="Q8" s="100"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="68"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
@@ -3446,26 +3432,26 @@
       <c r="AX8" s="9"/>
       <c r="AY8" s="10"/>
     </row>
-    <row r="9" spans="1:51" s="4" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="101" t="s">
+    <row r="9" spans="1:51" s="4" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A9" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="102"/>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="102"/>
-      <c r="H9" s="102"/>
-      <c r="I9" s="102"/>
-      <c r="J9" s="102"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="102"/>
-      <c r="N9" s="102"/>
-      <c r="O9" s="102"/>
-      <c r="P9" s="103"/>
-      <c r="Q9" s="104"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="70"/>
+      <c r="N9" s="70"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="72"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
@@ -3499,7 +3485,7 @@
       <c r="AX9" s="9"/>
       <c r="AY9" s="10"/>
     </row>
-    <row r="10" spans="1:51" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:51" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A10" s="11"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -3518,7 +3504,7 @@
       <c r="P10" s="12"/>
       <c r="Q10" s="12"/>
     </row>
-    <row r="11" spans="1:51" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:51" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="14" t="s">
         <v>4</v>
@@ -3539,7 +3525,7 @@
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
     </row>
-    <row r="12" spans="1:51" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:51" ht="21" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A12" s="13" t="s">
         <v>5</v>
       </c>
@@ -3560,15 +3546,15 @@
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
     </row>
-    <row r="13" spans="1:51" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:51" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A13" s="11"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="92"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
       <c r="D13" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="92"/>
-      <c r="F13" s="92"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="15" t="s">
         <v>7</v>
       </c>
@@ -3583,28 +3569,28 @@
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
     </row>
-    <row r="14" spans="1:51" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:51" ht="30" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A14" s="23"/>
-      <c r="B14" s="71" t="s">
+      <c r="B14" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="71"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="71"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-    </row>
-    <row r="15" spans="1:51" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="82"/>
+      <c r="L14" s="82"/>
+      <c r="M14" s="82"/>
+      <c r="N14" s="82"/>
+      <c r="O14" s="82"/>
+      <c r="P14" s="82"/>
+      <c r="Q14" s="82"/>
+    </row>
+    <row r="15" spans="1:51" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A15" s="11"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -3623,7 +3609,7 @@
       <c r="P15" s="16"/>
       <c r="Q15" s="16"/>
     </row>
-    <row r="16" spans="1:51" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:51" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11"/>
       <c r="B16" s="14" t="s">
         <v>4</v>
@@ -3644,7 +3630,7 @@
       <c r="P16" s="12"/>
       <c r="Q16" s="12"/>
     </row>
-    <row r="17" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A17" s="13" t="s">
         <v>9</v>
       </c>
@@ -3665,144 +3651,144 @@
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
     </row>
-    <row r="18" spans="1:17" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:17" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A18" s="13"/>
-      <c r="B18" s="72" t="s">
+      <c r="B18" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="72"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="72"/>
-      <c r="P18" s="72"/>
-      <c r="Q18" s="72"/>
-    </row>
-    <row r="19" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="62" t="s">
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="56"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="56"/>
+      <c r="P18" s="56"/>
+      <c r="Q18" s="56"/>
+    </row>
+    <row r="19" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A19" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="63"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="63"/>
-      <c r="N19" s="63"/>
-      <c r="O19" s="63"/>
-      <c r="P19" s="63"/>
-      <c r="Q19" s="64"/>
-    </row>
-    <row r="20" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="65"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="66"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="67"/>
-    </row>
-    <row r="21" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="65"/>
-      <c r="B21" s="66"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="66"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="66"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="67"/>
-    </row>
-    <row r="22" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="65"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="67"/>
-    </row>
-    <row r="23" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="65"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="66"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="67"/>
-    </row>
-    <row r="24" spans="1:17" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="68"/>
-      <c r="B24" s="69"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="69"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="69"/>
-      <c r="P24" s="69"/>
-      <c r="Q24" s="70"/>
-    </row>
-    <row r="25" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="74"/>
+      <c r="K19" s="74"/>
+      <c r="L19" s="74"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="74"/>
+      <c r="P19" s="74"/>
+      <c r="Q19" s="75"/>
+    </row>
+    <row r="20" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A20" s="76"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="77"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="77"/>
+      <c r="P20" s="77"/>
+      <c r="Q20" s="78"/>
+    </row>
+    <row r="21" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A21" s="76"/>
+      <c r="B21" s="77"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="77"/>
+      <c r="M21" s="77"/>
+      <c r="N21" s="77"/>
+      <c r="O21" s="77"/>
+      <c r="P21" s="77"/>
+      <c r="Q21" s="78"/>
+    </row>
+    <row r="22" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A22" s="76"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="77"/>
+      <c r="M22" s="77"/>
+      <c r="N22" s="77"/>
+      <c r="O22" s="77"/>
+      <c r="P22" s="77"/>
+      <c r="Q22" s="78"/>
+    </row>
+    <row r="23" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A23" s="76"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="77"/>
+      <c r="K23" s="77"/>
+      <c r="L23" s="77"/>
+      <c r="M23" s="77"/>
+      <c r="N23" s="77"/>
+      <c r="O23" s="77"/>
+      <c r="P23" s="77"/>
+      <c r="Q23" s="78"/>
+    </row>
+    <row r="24" spans="1:17" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A24" s="79"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="80"/>
+      <c r="K24" s="80"/>
+      <c r="L24" s="80"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="80"/>
+      <c r="O24" s="80"/>
+      <c r="P24" s="80"/>
+      <c r="Q24" s="81"/>
+    </row>
+    <row r="25" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -3821,7 +3807,7 @@
       <c r="P25" s="12"/>
       <c r="Q25" s="12"/>
     </row>
-    <row r="26" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11"/>
       <c r="B26" s="14" t="s">
         <v>12</v>
@@ -3842,7 +3828,7 @@
       <c r="P26" s="12"/>
       <c r="Q26" s="12"/>
     </row>
-    <row r="27" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A27" s="13" t="s">
         <v>13</v>
       </c>
@@ -3863,621 +3849,621 @@
       <c r="P27" s="12"/>
       <c r="Q27" s="12"/>
     </row>
-    <row r="28" spans="1:17" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:17" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A28" s="13"/>
-      <c r="B28" s="72" t="s">
+      <c r="B28" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="72"/>
-      <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
-    </row>
-    <row r="29" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="62" t="s">
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="56"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="56"/>
+      <c r="P28" s="56"/>
+      <c r="Q28" s="56"/>
+    </row>
+    <row r="29" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A29" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="63"/>
-      <c r="C29" s="63"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="63"/>
-      <c r="L29" s="63"/>
-      <c r="M29" s="63"/>
-      <c r="N29" s="63"/>
-      <c r="O29" s="63"/>
-      <c r="P29" s="63"/>
-      <c r="Q29" s="64"/>
-    </row>
-    <row r="30" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="65"/>
-      <c r="B30" s="73"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="73"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="73"/>
-      <c r="O30" s="73"/>
-      <c r="P30" s="73"/>
-      <c r="Q30" s="67"/>
-    </row>
-    <row r="31" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="65"/>
-      <c r="B31" s="73"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="73"/>
-      <c r="J31" s="73"/>
-      <c r="K31" s="73"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="73"/>
-      <c r="O31" s="73"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="67"/>
-    </row>
-    <row r="32" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="65"/>
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="73"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
-      <c r="J32" s="73"/>
-      <c r="K32" s="73"/>
-      <c r="L32" s="73"/>
-      <c r="M32" s="73"/>
-      <c r="N32" s="73"/>
-      <c r="O32" s="73"/>
-      <c r="P32" s="73"/>
-      <c r="Q32" s="67"/>
-    </row>
-    <row r="33" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="65"/>
-      <c r="B33" s="73"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="73"/>
-      <c r="H33" s="73"/>
-      <c r="I33" s="73"/>
-      <c r="J33" s="73"/>
-      <c r="K33" s="73"/>
-      <c r="L33" s="73"/>
-      <c r="M33" s="73"/>
-      <c r="N33" s="73"/>
-      <c r="O33" s="73"/>
-      <c r="P33" s="73"/>
-      <c r="Q33" s="67"/>
-    </row>
-    <row r="34" spans="1:17" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="68"/>
-      <c r="B34" s="69"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="69"/>
-      <c r="L34" s="69"/>
-      <c r="M34" s="69"/>
-      <c r="N34" s="69"/>
-      <c r="O34" s="69"/>
-      <c r="P34" s="69"/>
-      <c r="Q34" s="70"/>
-    </row>
-    <row r="35" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="39" t="s">
+      <c r="B29" s="74"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="74"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="74"/>
+      <c r="P29" s="74"/>
+      <c r="Q29" s="75"/>
+    </row>
+    <row r="30" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A30" s="76"/>
+      <c r="B30" s="77"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="77"/>
+      <c r="J30" s="77"/>
+      <c r="K30" s="77"/>
+      <c r="L30" s="77"/>
+      <c r="M30" s="77"/>
+      <c r="N30" s="77"/>
+      <c r="O30" s="77"/>
+      <c r="P30" s="77"/>
+      <c r="Q30" s="78"/>
+    </row>
+    <row r="31" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A31" s="76"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="77"/>
+      <c r="E31" s="77"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="77"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="77"/>
+      <c r="M31" s="77"/>
+      <c r="N31" s="77"/>
+      <c r="O31" s="77"/>
+      <c r="P31" s="77"/>
+      <c r="Q31" s="78"/>
+    </row>
+    <row r="32" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A32" s="76"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="77"/>
+      <c r="K32" s="77"/>
+      <c r="L32" s="77"/>
+      <c r="M32" s="77"/>
+      <c r="N32" s="77"/>
+      <c r="O32" s="77"/>
+      <c r="P32" s="77"/>
+      <c r="Q32" s="78"/>
+    </row>
+    <row r="33" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A33" s="76"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="77"/>
+      <c r="L33" s="77"/>
+      <c r="M33" s="77"/>
+      <c r="N33" s="77"/>
+      <c r="O33" s="77"/>
+      <c r="P33" s="77"/>
+      <c r="Q33" s="78"/>
+    </row>
+    <row r="34" spans="1:17" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A34" s="79"/>
+      <c r="B34" s="80"/>
+      <c r="C34" s="80"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="80"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="80"/>
+      <c r="M34" s="80"/>
+      <c r="N34" s="80"/>
+      <c r="O34" s="80"/>
+      <c r="P34" s="80"/>
+      <c r="Q34" s="81"/>
+    </row>
+    <row r="35" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A35" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-    </row>
-    <row r="36" spans="1:17" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="33"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-    </row>
-    <row r="37" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="35"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="32"/>
+    </row>
+    <row r="36" spans="1:17" ht="2.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A36" s="31"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+    </row>
+    <row r="37" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="33"/>
       <c r="B37" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-    </row>
-    <row r="38" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="40" t="s">
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+    </row>
+    <row r="38" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A38" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="41"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="41"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="41"/>
-      <c r="N38" s="41"/>
-      <c r="O38" s="41"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-    </row>
-    <row r="39" spans="1:17" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="40"/>
-      <c r="B39" s="76" t="s">
+      <c r="B38" s="39"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="39"/>
+      <c r="Q38" s="39"/>
+    </row>
+    <row r="39" spans="1:17" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A39" s="38"/>
+      <c r="B39" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="76"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
-      <c r="I39" s="76"/>
-      <c r="J39" s="76"/>
-      <c r="K39" s="76"/>
-      <c r="L39" s="76"/>
-      <c r="M39" s="76"/>
-      <c r="N39" s="76"/>
-      <c r="O39" s="76"/>
-      <c r="P39" s="76"/>
-      <c r="Q39" s="76"/>
-    </row>
-    <row r="40" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="77"/>
-      <c r="B40" s="78"/>
-      <c r="C40" s="78"/>
-      <c r="D40" s="78"/>
-      <c r="E40" s="78"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="78"/>
-      <c r="L40" s="78"/>
-      <c r="M40" s="78"/>
-      <c r="N40" s="78"/>
-      <c r="O40" s="78"/>
-      <c r="P40" s="78"/>
-      <c r="Q40" s="79"/>
-    </row>
-    <row r="41" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="80"/>
-      <c r="B41" s="81"/>
-      <c r="C41" s="81"/>
-      <c r="D41" s="81"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81"/>
-      <c r="H41" s="81"/>
-      <c r="I41" s="81"/>
-      <c r="J41" s="81"/>
-      <c r="K41" s="81"/>
-      <c r="L41" s="81"/>
-      <c r="M41" s="81"/>
-      <c r="N41" s="81"/>
-      <c r="O41" s="81"/>
-      <c r="P41" s="81"/>
-      <c r="Q41" s="82"/>
-    </row>
-    <row r="42" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="80"/>
-      <c r="B42" s="81"/>
-      <c r="C42" s="81"/>
-      <c r="D42" s="81"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="81"/>
-      <c r="I42" s="81"/>
-      <c r="J42" s="81"/>
-      <c r="K42" s="81"/>
-      <c r="L42" s="81"/>
-      <c r="M42" s="81"/>
-      <c r="N42" s="81"/>
-      <c r="O42" s="81"/>
-      <c r="P42" s="81"/>
-      <c r="Q42" s="82"/>
-    </row>
-    <row r="43" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="80"/>
-      <c r="B43" s="83"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="83"/>
-      <c r="J43" s="83"/>
-      <c r="K43" s="83"/>
-      <c r="L43" s="83"/>
-      <c r="M43" s="83"/>
-      <c r="N43" s="83"/>
-      <c r="O43" s="83"/>
-      <c r="P43" s="83"/>
-      <c r="Q43" s="82"/>
-    </row>
-    <row r="44" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="80"/>
-      <c r="B44" s="83"/>
-      <c r="C44" s="83"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="83"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="83"/>
-      <c r="J44" s="83"/>
-      <c r="K44" s="83"/>
-      <c r="L44" s="83"/>
-      <c r="M44" s="83"/>
-      <c r="N44" s="83"/>
-      <c r="O44" s="83"/>
-      <c r="P44" s="83"/>
-      <c r="Q44" s="82"/>
-    </row>
-    <row r="45" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="80"/>
-      <c r="B45" s="83"/>
-      <c r="C45" s="83"/>
-      <c r="D45" s="83"/>
-      <c r="E45" s="83"/>
-      <c r="F45" s="83"/>
-      <c r="G45" s="83"/>
-      <c r="H45" s="83"/>
-      <c r="I45" s="83"/>
-      <c r="J45" s="83"/>
-      <c r="K45" s="83"/>
-      <c r="L45" s="83"/>
-      <c r="M45" s="83"/>
-      <c r="N45" s="83"/>
-      <c r="O45" s="83"/>
-      <c r="P45" s="83"/>
-      <c r="Q45" s="82"/>
-    </row>
-    <row r="46" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="80"/>
-      <c r="B46" s="83"/>
-      <c r="C46" s="83"/>
-      <c r="D46" s="83"/>
-      <c r="E46" s="83"/>
-      <c r="F46" s="83"/>
-      <c r="G46" s="83"/>
-      <c r="H46" s="83"/>
-      <c r="I46" s="83"/>
-      <c r="J46" s="83"/>
-      <c r="K46" s="83"/>
-      <c r="L46" s="83"/>
-      <c r="M46" s="83"/>
-      <c r="N46" s="83"/>
-      <c r="O46" s="83"/>
-      <c r="P46" s="83"/>
-      <c r="Q46" s="82"/>
-    </row>
-    <row r="47" spans="1:17" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="84"/>
-      <c r="B47" s="85"/>
-      <c r="C47" s="85"/>
-      <c r="D47" s="85"/>
-      <c r="E47" s="85"/>
-      <c r="F47" s="85"/>
-      <c r="G47" s="85"/>
-      <c r="H47" s="85"/>
-      <c r="I47" s="85"/>
-      <c r="J47" s="85"/>
-      <c r="K47" s="85"/>
-      <c r="L47" s="85"/>
-      <c r="M47" s="85"/>
-      <c r="N47" s="85"/>
-      <c r="O47" s="85"/>
-      <c r="P47" s="85"/>
-      <c r="Q47" s="86"/>
-    </row>
-    <row r="48" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="52" t="s">
+      <c r="C39" s="85"/>
+      <c r="D39" s="85"/>
+      <c r="E39" s="85"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="85"/>
+      <c r="H39" s="85"/>
+      <c r="I39" s="85"/>
+      <c r="J39" s="85"/>
+      <c r="K39" s="85"/>
+      <c r="L39" s="85"/>
+      <c r="M39" s="85"/>
+      <c r="N39" s="85"/>
+      <c r="O39" s="85"/>
+      <c r="P39" s="85"/>
+      <c r="Q39" s="85"/>
+    </row>
+    <row r="40" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A40" s="86"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="87"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="87"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="87"/>
+      <c r="I40" s="87"/>
+      <c r="J40" s="87"/>
+      <c r="K40" s="87"/>
+      <c r="L40" s="87"/>
+      <c r="M40" s="87"/>
+      <c r="N40" s="87"/>
+      <c r="O40" s="87"/>
+      <c r="P40" s="87"/>
+      <c r="Q40" s="88"/>
+    </row>
+    <row r="41" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A41" s="89"/>
+      <c r="B41" s="90"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="90"/>
+      <c r="H41" s="90"/>
+      <c r="I41" s="90"/>
+      <c r="J41" s="90"/>
+      <c r="K41" s="90"/>
+      <c r="L41" s="90"/>
+      <c r="M41" s="90"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="90"/>
+      <c r="P41" s="90"/>
+      <c r="Q41" s="91"/>
+    </row>
+    <row r="42" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A42" s="89"/>
+      <c r="B42" s="90"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="90"/>
+      <c r="F42" s="90"/>
+      <c r="G42" s="90"/>
+      <c r="H42" s="90"/>
+      <c r="I42" s="90"/>
+      <c r="J42" s="90"/>
+      <c r="K42" s="90"/>
+      <c r="L42" s="90"/>
+      <c r="M42" s="90"/>
+      <c r="N42" s="90"/>
+      <c r="O42" s="90"/>
+      <c r="P42" s="90"/>
+      <c r="Q42" s="91"/>
+    </row>
+    <row r="43" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A43" s="89"/>
+      <c r="B43" s="90"/>
+      <c r="C43" s="90"/>
+      <c r="D43" s="90"/>
+      <c r="E43" s="90"/>
+      <c r="F43" s="90"/>
+      <c r="G43" s="90"/>
+      <c r="H43" s="90"/>
+      <c r="I43" s="90"/>
+      <c r="J43" s="90"/>
+      <c r="K43" s="90"/>
+      <c r="L43" s="90"/>
+      <c r="M43" s="90"/>
+      <c r="N43" s="90"/>
+      <c r="O43" s="90"/>
+      <c r="P43" s="90"/>
+      <c r="Q43" s="91"/>
+    </row>
+    <row r="44" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A44" s="89"/>
+      <c r="B44" s="90"/>
+      <c r="C44" s="90"/>
+      <c r="D44" s="90"/>
+      <c r="E44" s="90"/>
+      <c r="F44" s="90"/>
+      <c r="G44" s="90"/>
+      <c r="H44" s="90"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="90"/>
+      <c r="K44" s="90"/>
+      <c r="L44" s="90"/>
+      <c r="M44" s="90"/>
+      <c r="N44" s="90"/>
+      <c r="O44" s="90"/>
+      <c r="P44" s="90"/>
+      <c r="Q44" s="91"/>
+    </row>
+    <row r="45" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A45" s="89"/>
+      <c r="B45" s="90"/>
+      <c r="C45" s="90"/>
+      <c r="D45" s="90"/>
+      <c r="E45" s="90"/>
+      <c r="F45" s="90"/>
+      <c r="G45" s="90"/>
+      <c r="H45" s="90"/>
+      <c r="I45" s="90"/>
+      <c r="J45" s="90"/>
+      <c r="K45" s="90"/>
+      <c r="L45" s="90"/>
+      <c r="M45" s="90"/>
+      <c r="N45" s="90"/>
+      <c r="O45" s="90"/>
+      <c r="P45" s="90"/>
+      <c r="Q45" s="91"/>
+    </row>
+    <row r="46" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A46" s="89"/>
+      <c r="B46" s="90"/>
+      <c r="C46" s="90"/>
+      <c r="D46" s="90"/>
+      <c r="E46" s="90"/>
+      <c r="F46" s="90"/>
+      <c r="G46" s="90"/>
+      <c r="H46" s="90"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="90"/>
+      <c r="K46" s="90"/>
+      <c r="L46" s="90"/>
+      <c r="M46" s="90"/>
+      <c r="N46" s="90"/>
+      <c r="O46" s="90"/>
+      <c r="P46" s="90"/>
+      <c r="Q46" s="91"/>
+    </row>
+    <row r="47" spans="1:17" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A47" s="92"/>
+      <c r="B47" s="93"/>
+      <c r="C47" s="93"/>
+      <c r="D47" s="93"/>
+      <c r="E47" s="93"/>
+      <c r="F47" s="93"/>
+      <c r="G47" s="93"/>
+      <c r="H47" s="93"/>
+      <c r="I47" s="93"/>
+      <c r="J47" s="93"/>
+      <c r="K47" s="93"/>
+      <c r="L47" s="93"/>
+      <c r="M47" s="93"/>
+      <c r="N47" s="93"/>
+      <c r="O47" s="93"/>
+      <c r="P47" s="93"/>
+      <c r="Q47" s="94"/>
+    </row>
+    <row r="48" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A48" s="107" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="49" t="s">
+      <c r="B48" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
-      <c r="K48" s="49"/>
-      <c r="L48" s="49"/>
-      <c r="M48" s="49"/>
-      <c r="N48" s="49"/>
-      <c r="O48" s="49"/>
-      <c r="P48" s="46"/>
-      <c r="Q48" s="46"/>
-    </row>
-    <row r="49" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="53"/>
-      <c r="B49" s="50"/>
-      <c r="C49" s="50"/>
-      <c r="D49" s="50"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="50"/>
-      <c r="H49" s="50"/>
-      <c r="I49" s="50"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="50"/>
-      <c r="L49" s="50"/>
-      <c r="M49" s="50"/>
-      <c r="N49" s="50"/>
-      <c r="O49" s="50"/>
-      <c r="P49" s="47"/>
-      <c r="Q49" s="47"/>
-    </row>
-    <row r="50" spans="1:18" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="54"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="51"/>
-      <c r="J50" s="51"/>
-      <c r="K50" s="51"/>
-      <c r="L50" s="51"/>
-      <c r="M50" s="51"/>
-      <c r="N50" s="51"/>
-      <c r="O50" s="51"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="48"/>
-    </row>
-    <row r="51" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="36"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="36"/>
-      <c r="D51" s="36"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="36"/>
-      <c r="G51" s="36"/>
-      <c r="H51" s="36"/>
-      <c r="I51" s="36"/>
-      <c r="J51" s="36"/>
-      <c r="K51" s="36"/>
-      <c r="L51" s="36"/>
-      <c r="M51" s="36"/>
-      <c r="N51" s="36"/>
-      <c r="O51" s="36"/>
-      <c r="P51" s="37"/>
-      <c r="Q51" s="37"/>
+      <c r="C48" s="104"/>
+      <c r="D48" s="104"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="104"/>
+      <c r="K48" s="104"/>
+      <c r="L48" s="104"/>
+      <c r="M48" s="104"/>
+      <c r="N48" s="104"/>
+      <c r="O48" s="104"/>
+      <c r="P48" s="101"/>
+      <c r="Q48" s="101"/>
+    </row>
+    <row r="49" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A49" s="108"/>
+      <c r="B49" s="105"/>
+      <c r="C49" s="105"/>
+      <c r="D49" s="105"/>
+      <c r="E49" s="105"/>
+      <c r="F49" s="105"/>
+      <c r="G49" s="105"/>
+      <c r="H49" s="105"/>
+      <c r="I49" s="105"/>
+      <c r="J49" s="105"/>
+      <c r="K49" s="105"/>
+      <c r="L49" s="105"/>
+      <c r="M49" s="105"/>
+      <c r="N49" s="105"/>
+      <c r="O49" s="105"/>
+      <c r="P49" s="102"/>
+      <c r="Q49" s="102"/>
+    </row>
+    <row r="50" spans="1:18" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A50" s="109"/>
+      <c r="B50" s="106"/>
+      <c r="C50" s="106"/>
+      <c r="D50" s="106"/>
+      <c r="E50" s="106"/>
+      <c r="F50" s="106"/>
+      <c r="G50" s="106"/>
+      <c r="H50" s="106"/>
+      <c r="I50" s="106"/>
+      <c r="J50" s="106"/>
+      <c r="K50" s="106"/>
+      <c r="L50" s="106"/>
+      <c r="M50" s="106"/>
+      <c r="N50" s="106"/>
+      <c r="O50" s="106"/>
+      <c r="P50" s="103"/>
+      <c r="Q50" s="103"/>
+    </row>
+    <row r="51" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A51" s="34"/>
+      <c r="B51" s="34"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="34"/>
+      <c r="L51" s="34"/>
+      <c r="M51" s="34"/>
+      <c r="N51" s="34"/>
+      <c r="O51" s="34"/>
+      <c r="P51" s="35"/>
+      <c r="Q51" s="35"/>
       <c r="R51" s="12"/>
     </row>
-    <row r="52" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="40" t="s">
+    <row r="52" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A52" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="B52" s="41"/>
-      <c r="C52" s="40"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="41"/>
-      <c r="J52" s="41"/>
-      <c r="K52" s="41"/>
-      <c r="L52" s="41"/>
-      <c r="M52" s="41"/>
-      <c r="N52" s="41"/>
-      <c r="O52" s="41"/>
-      <c r="P52" s="41"/>
-      <c r="Q52" s="41"/>
-    </row>
-    <row r="53" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="55" t="s">
+      <c r="B52" s="39"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="39"/>
+      <c r="J52" s="39"/>
+      <c r="K52" s="39"/>
+      <c r="L52" s="39"/>
+      <c r="M52" s="39"/>
+      <c r="N52" s="39"/>
+      <c r="O52" s="39"/>
+      <c r="P52" s="39"/>
+      <c r="Q52" s="39"/>
+    </row>
+    <row r="53" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A53" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="B53" s="55"/>
-      <c r="C53" s="55"/>
-      <c r="D53" s="55"/>
-      <c r="E53" s="55"/>
-      <c r="F53" s="55" t="s">
+      <c r="B53" s="98"/>
+      <c r="C53" s="98"/>
+      <c r="D53" s="98"/>
+      <c r="E53" s="98"/>
+      <c r="F53" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="G53" s="55"/>
-      <c r="H53" s="55"/>
-      <c r="I53" s="55"/>
-      <c r="J53" s="55"/>
-      <c r="K53" s="55"/>
-      <c r="L53" s="55"/>
-      <c r="M53" s="55"/>
-      <c r="N53" s="55"/>
-      <c r="O53" s="55"/>
-      <c r="P53" s="55"/>
-      <c r="Q53" s="55"/>
-    </row>
-    <row r="54" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="58" t="s">
+      <c r="G53" s="98"/>
+      <c r="H53" s="98"/>
+      <c r="I53" s="98"/>
+      <c r="J53" s="98"/>
+      <c r="K53" s="98"/>
+      <c r="L53" s="98"/>
+      <c r="M53" s="98"/>
+      <c r="N53" s="98"/>
+      <c r="O53" s="98"/>
+      <c r="P53" s="98"/>
+      <c r="Q53" s="98"/>
+    </row>
+    <row r="54" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A54" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="B54" s="58"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="55"/>
-      <c r="G54" s="55"/>
-      <c r="H54" s="55"/>
-      <c r="I54" s="55"/>
-      <c r="J54" s="55"/>
-      <c r="K54" s="55"/>
-      <c r="L54" s="55"/>
-      <c r="M54" s="55"/>
-      <c r="N54" s="55"/>
-      <c r="O54" s="55"/>
-      <c r="P54" s="55"/>
-      <c r="Q54" s="55"/>
-    </row>
-    <row r="55" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="58"/>
-      <c r="B55" s="58"/>
-      <c r="C55" s="58"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="58"/>
-      <c r="F55" s="55"/>
-      <c r="G55" s="55"/>
-      <c r="H55" s="55"/>
-      <c r="I55" s="55"/>
-      <c r="J55" s="55"/>
-      <c r="K55" s="55"/>
-      <c r="L55" s="55"/>
-      <c r="M55" s="55"/>
-      <c r="N55" s="55"/>
-      <c r="O55" s="55"/>
-      <c r="P55" s="55"/>
-      <c r="Q55" s="55"/>
-    </row>
-    <row r="56" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="58"/>
-      <c r="B56" s="58"/>
-      <c r="C56" s="58"/>
-      <c r="D56" s="58"/>
-      <c r="E56" s="58"/>
-      <c r="F56" s="55"/>
-      <c r="G56" s="55"/>
-      <c r="H56" s="55"/>
-      <c r="I56" s="55"/>
-      <c r="J56" s="55"/>
-      <c r="K56" s="55"/>
-      <c r="L56" s="55"/>
-      <c r="M56" s="55"/>
-      <c r="N56" s="55"/>
-      <c r="O56" s="55"/>
-      <c r="P56" s="55"/>
-      <c r="Q56" s="55"/>
-    </row>
-    <row r="57" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="58"/>
-      <c r="B57" s="58"/>
-      <c r="C57" s="58"/>
-      <c r="D57" s="58"/>
-      <c r="E57" s="58"/>
-      <c r="F57" s="55"/>
-      <c r="G57" s="55"/>
-      <c r="H57" s="55"/>
-      <c r="I57" s="55"/>
-      <c r="J57" s="55"/>
-      <c r="K57" s="55"/>
-      <c r="L57" s="55"/>
-      <c r="M57" s="55"/>
-      <c r="N57" s="55"/>
-      <c r="O57" s="55"/>
-      <c r="P57" s="55"/>
-      <c r="Q57" s="55"/>
-    </row>
-    <row r="58" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="58"/>
-      <c r="B58" s="58"/>
-      <c r="C58" s="58"/>
-      <c r="D58" s="58"/>
-      <c r="E58" s="58"/>
-      <c r="F58" s="55"/>
-      <c r="G58" s="55"/>
-      <c r="H58" s="55"/>
-      <c r="I58" s="55"/>
-      <c r="J58" s="55"/>
-      <c r="K58" s="55"/>
-      <c r="L58" s="55"/>
-      <c r="M58" s="55"/>
-      <c r="N58" s="55"/>
-      <c r="O58" s="55"/>
-      <c r="P58" s="55"/>
-      <c r="Q58" s="55"/>
-    </row>
-    <row r="59" spans="1:18" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B54" s="99"/>
+      <c r="C54" s="99"/>
+      <c r="D54" s="99"/>
+      <c r="E54" s="99"/>
+      <c r="F54" s="98"/>
+      <c r="G54" s="98"/>
+      <c r="H54" s="98"/>
+      <c r="I54" s="98"/>
+      <c r="J54" s="98"/>
+      <c r="K54" s="98"/>
+      <c r="L54" s="98"/>
+      <c r="M54" s="98"/>
+      <c r="N54" s="98"/>
+      <c r="O54" s="98"/>
+      <c r="P54" s="98"/>
+      <c r="Q54" s="98"/>
+    </row>
+    <row r="55" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A55" s="99"/>
+      <c r="B55" s="99"/>
+      <c r="C55" s="99"/>
+      <c r="D55" s="99"/>
+      <c r="E55" s="99"/>
+      <c r="F55" s="98"/>
+      <c r="G55" s="98"/>
+      <c r="H55" s="98"/>
+      <c r="I55" s="98"/>
+      <c r="J55" s="98"/>
+      <c r="K55" s="98"/>
+      <c r="L55" s="98"/>
+      <c r="M55" s="98"/>
+      <c r="N55" s="98"/>
+      <c r="O55" s="98"/>
+      <c r="P55" s="98"/>
+      <c r="Q55" s="98"/>
+    </row>
+    <row r="56" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A56" s="99"/>
+      <c r="B56" s="99"/>
+      <c r="C56" s="99"/>
+      <c r="D56" s="99"/>
+      <c r="E56" s="99"/>
+      <c r="F56" s="98"/>
+      <c r="G56" s="98"/>
+      <c r="H56" s="98"/>
+      <c r="I56" s="98"/>
+      <c r="J56" s="98"/>
+      <c r="K56" s="98"/>
+      <c r="L56" s="98"/>
+      <c r="M56" s="98"/>
+      <c r="N56" s="98"/>
+      <c r="O56" s="98"/>
+      <c r="P56" s="98"/>
+      <c r="Q56" s="98"/>
+    </row>
+    <row r="57" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A57" s="99"/>
+      <c r="B57" s="99"/>
+      <c r="C57" s="99"/>
+      <c r="D57" s="99"/>
+      <c r="E57" s="99"/>
+      <c r="F57" s="98"/>
+      <c r="G57" s="98"/>
+      <c r="H57" s="98"/>
+      <c r="I57" s="98"/>
+      <c r="J57" s="98"/>
+      <c r="K57" s="98"/>
+      <c r="L57" s="98"/>
+      <c r="M57" s="98"/>
+      <c r="N57" s="98"/>
+      <c r="O57" s="98"/>
+      <c r="P57" s="98"/>
+      <c r="Q57" s="98"/>
+    </row>
+    <row r="58" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A58" s="99"/>
+      <c r="B58" s="99"/>
+      <c r="C58" s="99"/>
+      <c r="D58" s="99"/>
+      <c r="E58" s="99"/>
+      <c r="F58" s="98"/>
+      <c r="G58" s="98"/>
+      <c r="H58" s="98"/>
+      <c r="I58" s="98"/>
+      <c r="J58" s="98"/>
+      <c r="K58" s="98"/>
+      <c r="L58" s="98"/>
+      <c r="M58" s="98"/>
+      <c r="N58" s="98"/>
+      <c r="O58" s="98"/>
+      <c r="P58" s="98"/>
+      <c r="Q58" s="98"/>
+    </row>
+    <row r="59" spans="1:18" ht="8.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A59" s="17"/>
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
@@ -4496,262 +4482,262 @@
       <c r="P59" s="17"/>
       <c r="Q59" s="17"/>
     </row>
-    <row r="60" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A60" s="17"/>
-      <c r="B60" s="42" t="s">
+      <c r="B60" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C60" s="43"/>
-      <c r="D60" s="43"/>
-      <c r="E60" s="43"/>
-      <c r="F60" s="43"/>
-      <c r="G60" s="43"/>
-      <c r="H60" s="43"/>
-      <c r="I60" s="43"/>
-      <c r="J60" s="43"/>
-      <c r="K60" s="43"/>
-      <c r="L60" s="43"/>
-      <c r="M60" s="43"/>
-      <c r="N60" s="43"/>
-      <c r="O60" s="43"/>
-      <c r="P60" s="43"/>
-      <c r="Q60" s="43"/>
-    </row>
-    <row r="61" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C60" s="41"/>
+      <c r="D60" s="41"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="41"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="41"/>
+      <c r="I60" s="41"/>
+      <c r="J60" s="41"/>
+      <c r="K60" s="41"/>
+      <c r="L60" s="41"/>
+      <c r="M60" s="41"/>
+      <c r="N60" s="41"/>
+      <c r="O60" s="41"/>
+      <c r="P60" s="41"/>
+      <c r="Q60" s="41"/>
+    </row>
+    <row r="61" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A61" s="17"/>
-      <c r="B61" s="43"/>
-      <c r="C61" s="43"/>
-      <c r="D61" s="43"/>
-      <c r="E61" s="43"/>
-      <c r="F61" s="43"/>
-      <c r="G61" s="43"/>
-      <c r="H61" s="87"/>
-      <c r="I61" s="87"/>
-      <c r="J61" s="87"/>
-      <c r="K61" s="44" t="s">
+      <c r="B61" s="41"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="41"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="95"/>
+      <c r="I61" s="95"/>
+      <c r="J61" s="95"/>
+      <c r="K61" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="L61" s="88"/>
-      <c r="M61" s="88"/>
-      <c r="N61" s="44" t="s">
+      <c r="L61" s="96"/>
+      <c r="M61" s="96"/>
+      <c r="N61" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="O61" s="88"/>
-      <c r="P61" s="88"/>
-      <c r="Q61" s="44" t="s">
+      <c r="O61" s="96"/>
+      <c r="P61" s="96"/>
+      <c r="Q61" s="42" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A62" s="17"/>
-      <c r="B62" s="43"/>
-      <c r="C62" s="43"/>
-      <c r="D62" s="43"/>
-      <c r="E62" s="43"/>
-      <c r="F62" s="43"/>
-      <c r="G62" s="43"/>
-      <c r="H62" s="42" t="s">
+      <c r="B62" s="41"/>
+      <c r="C62" s="41"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="41"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="I62" s="43"/>
-      <c r="J62" s="43"/>
-      <c r="K62" s="43"/>
-      <c r="L62" s="43"/>
-      <c r="M62" s="43"/>
-      <c r="N62" s="43"/>
-      <c r="O62" s="43"/>
-      <c r="P62" s="43"/>
-      <c r="Q62" s="43"/>
-    </row>
-    <row r="63" spans="1:18" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I62" s="41"/>
+      <c r="J62" s="41"/>
+      <c r="K62" s="41"/>
+      <c r="L62" s="41"/>
+      <c r="M62" s="41"/>
+      <c r="N62" s="41"/>
+      <c r="O62" s="41"/>
+      <c r="P62" s="41"/>
+      <c r="Q62" s="41"/>
+    </row>
+    <row r="63" spans="1:18" ht="8.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A63" s="17"/>
-      <c r="B63" s="43"/>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
-      <c r="E63" s="43"/>
-      <c r="F63" s="43"/>
-      <c r="G63" s="43"/>
-      <c r="H63" s="43"/>
-      <c r="I63" s="43"/>
-      <c r="J63" s="43"/>
-      <c r="K63" s="43"/>
-      <c r="L63" s="43"/>
-      <c r="M63" s="43"/>
-      <c r="N63" s="43"/>
-      <c r="O63" s="43"/>
-      <c r="P63" s="43"/>
-      <c r="Q63" s="43"/>
-    </row>
-    <row r="64" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="41"/>
+      <c r="G63" s="41"/>
+      <c r="H63" s="41"/>
+      <c r="I63" s="41"/>
+      <c r="J63" s="41"/>
+      <c r="K63" s="41"/>
+      <c r="L63" s="41"/>
+      <c r="M63" s="41"/>
+      <c r="N63" s="41"/>
+      <c r="O63" s="41"/>
+      <c r="P63" s="41"/>
+      <c r="Q63" s="41"/>
+    </row>
+    <row r="64" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A64" s="17"/>
-      <c r="B64" s="43"/>
-      <c r="C64" s="43"/>
-      <c r="D64" s="43"/>
-      <c r="E64" s="43"/>
-      <c r="F64" s="43"/>
-      <c r="G64" s="43"/>
-      <c r="H64" s="59" t="s">
+      <c r="B64" s="41"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="41"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="I64" s="59"/>
-      <c r="J64" s="59"/>
-      <c r="K64" s="60"/>
-      <c r="L64" s="60"/>
-      <c r="M64" s="60"/>
-      <c r="N64" s="60"/>
-      <c r="O64" s="60"/>
-      <c r="P64" s="60"/>
-      <c r="Q64" s="60"/>
-    </row>
-    <row r="65" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I64" s="45"/>
+      <c r="J64" s="45"/>
+      <c r="K64" s="46"/>
+      <c r="L64" s="46"/>
+      <c r="M64" s="46"/>
+      <c r="N64" s="46"/>
+      <c r="O64" s="46"/>
+      <c r="P64" s="46"/>
+      <c r="Q64" s="46"/>
+    </row>
+    <row r="65" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A65" s="17"/>
-      <c r="B65" s="43"/>
-      <c r="C65" s="43"/>
-      <c r="D65" s="43"/>
-      <c r="E65" s="43"/>
-      <c r="F65" s="43"/>
-      <c r="G65" s="43"/>
-      <c r="H65" s="59" t="s">
+      <c r="B65" s="41"/>
+      <c r="C65" s="41"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="41"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="I65" s="59"/>
-      <c r="J65" s="59"/>
-      <c r="K65" s="60"/>
-      <c r="L65" s="60"/>
-      <c r="M65" s="60"/>
-      <c r="N65" s="60"/>
-      <c r="O65" s="60"/>
-      <c r="P65" s="60"/>
-      <c r="Q65" s="60"/>
-    </row>
-    <row r="66" spans="1:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I65" s="45"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="46"/>
+      <c r="L65" s="46"/>
+      <c r="M65" s="46"/>
+      <c r="N65" s="46"/>
+      <c r="O65" s="46"/>
+      <c r="P65" s="46"/>
+      <c r="Q65" s="46"/>
+    </row>
+    <row r="66" spans="1:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A66" s="17"/>
-      <c r="B66" s="43"/>
-      <c r="C66" s="43"/>
-      <c r="D66" s="43"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43"/>
-      <c r="G66" s="43"/>
-      <c r="H66" s="59" t="s">
+      <c r="B66" s="41"/>
+      <c r="C66" s="41"/>
+      <c r="D66" s="41"/>
+      <c r="E66" s="41"/>
+      <c r="F66" s="41"/>
+      <c r="G66" s="41"/>
+      <c r="H66" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="I66" s="59"/>
-      <c r="J66" s="59"/>
-      <c r="K66" s="60"/>
-      <c r="L66" s="60"/>
-      <c r="M66" s="60"/>
-      <c r="N66" s="60"/>
-      <c r="O66" s="60"/>
-      <c r="P66" s="60"/>
-      <c r="Q66" s="60"/>
-    </row>
-    <row r="67" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I66" s="45"/>
+      <c r="J66" s="45"/>
+      <c r="K66" s="46"/>
+      <c r="L66" s="46"/>
+      <c r="M66" s="46"/>
+      <c r="N66" s="46"/>
+      <c r="O66" s="46"/>
+      <c r="P66" s="46"/>
+      <c r="Q66" s="46"/>
+    </row>
+    <row r="67" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A67" s="17"/>
-      <c r="B67" s="43"/>
-      <c r="C67" s="43"/>
-      <c r="D67" s="43"/>
-      <c r="E67" s="43"/>
-      <c r="F67" s="43"/>
-      <c r="G67" s="43"/>
-      <c r="H67" s="59" t="s">
+      <c r="B67" s="41"/>
+      <c r="C67" s="41"/>
+      <c r="D67" s="41"/>
+      <c r="E67" s="41"/>
+      <c r="F67" s="41"/>
+      <c r="G67" s="41"/>
+      <c r="H67" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="I67" s="59"/>
-      <c r="J67" s="59"/>
-      <c r="K67" s="60"/>
-      <c r="L67" s="60"/>
-      <c r="M67" s="60"/>
-      <c r="N67" s="60"/>
-      <c r="O67" s="60"/>
-      <c r="P67" s="60"/>
-      <c r="Q67" s="60"/>
-    </row>
-    <row r="68" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I67" s="45"/>
+      <c r="J67" s="45"/>
+      <c r="K67" s="46"/>
+      <c r="L67" s="46"/>
+      <c r="M67" s="46"/>
+      <c r="N67" s="46"/>
+      <c r="O67" s="46"/>
+      <c r="P67" s="46"/>
+      <c r="Q67" s="46"/>
+    </row>
+    <row r="68" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A68" s="17"/>
-      <c r="B68" s="43"/>
-      <c r="C68" s="43"/>
-      <c r="D68" s="43"/>
-      <c r="E68" s="43"/>
-      <c r="F68" s="43"/>
-      <c r="G68" s="43"/>
-      <c r="H68" s="59" t="s">
+      <c r="B68" s="41"/>
+      <c r="C68" s="41"/>
+      <c r="D68" s="41"/>
+      <c r="E68" s="41"/>
+      <c r="F68" s="41"/>
+      <c r="G68" s="41"/>
+      <c r="H68" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="I68" s="59"/>
-      <c r="J68" s="59"/>
-      <c r="K68" s="60"/>
-      <c r="L68" s="60"/>
-      <c r="M68" s="60"/>
-      <c r="N68" s="60"/>
-      <c r="O68" s="60"/>
-      <c r="P68" s="60"/>
-      <c r="Q68" s="60"/>
-      <c r="S68" s="30"/>
-    </row>
-    <row r="69" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I68" s="45"/>
+      <c r="J68" s="45"/>
+      <c r="K68" s="46"/>
+      <c r="L68" s="46"/>
+      <c r="M68" s="46"/>
+      <c r="N68" s="46"/>
+      <c r="O68" s="46"/>
+      <c r="P68" s="46"/>
+      <c r="Q68" s="46"/>
+      <c r="S68" s="29"/>
+    </row>
+    <row r="69" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A69" s="17"/>
-      <c r="B69" s="43"/>
-      <c r="C69" s="43"/>
-      <c r="D69" s="43"/>
-      <c r="E69" s="43"/>
-      <c r="F69" s="43"/>
-      <c r="G69" s="43"/>
-      <c r="H69" s="59" t="s">
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="41"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="I69" s="59"/>
-      <c r="J69" s="59"/>
-      <c r="K69" s="60"/>
-      <c r="L69" s="60"/>
-      <c r="M69" s="60"/>
-      <c r="N69" s="60"/>
-      <c r="O69" s="60"/>
-      <c r="P69" s="60"/>
-      <c r="Q69" s="60"/>
-    </row>
-    <row r="70" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I69" s="45"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="46"/>
+      <c r="L69" s="46"/>
+      <c r="M69" s="46"/>
+      <c r="N69" s="46"/>
+      <c r="O69" s="46"/>
+      <c r="P69" s="46"/>
+      <c r="Q69" s="46"/>
+    </row>
+    <row r="70" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A70" s="17"/>
-      <c r="B70" s="43"/>
-      <c r="C70" s="43"/>
-      <c r="D70" s="43"/>
-      <c r="E70" s="43"/>
-      <c r="F70" s="43"/>
-      <c r="G70" s="43"/>
-      <c r="H70" s="59" t="s">
+      <c r="B70" s="41"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="41"/>
+      <c r="E70" s="41"/>
+      <c r="F70" s="41"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="I70" s="59"/>
-      <c r="J70" s="59"/>
-      <c r="K70" s="60"/>
-      <c r="L70" s="60"/>
-      <c r="M70" s="60"/>
-      <c r="N70" s="60"/>
-      <c r="O70" s="60"/>
-      <c r="P70" s="60"/>
-      <c r="Q70" s="60"/>
-    </row>
-    <row r="71" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I70" s="45"/>
+      <c r="J70" s="45"/>
+      <c r="K70" s="46"/>
+      <c r="L70" s="46"/>
+      <c r="M70" s="46"/>
+      <c r="N70" s="46"/>
+      <c r="O70" s="46"/>
+      <c r="P70" s="46"/>
+      <c r="Q70" s="46"/>
+    </row>
+    <row r="71" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A71" s="17"/>
-      <c r="B71" s="43"/>
-      <c r="C71" s="43"/>
-      <c r="D71" s="43"/>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
-      <c r="G71" s="43"/>
-      <c r="H71" s="59" t="s">
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="41"/>
+      <c r="F71" s="41"/>
+      <c r="G71" s="41"/>
+      <c r="H71" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="I71" s="59"/>
-      <c r="J71" s="59"/>
-      <c r="K71" s="60"/>
-      <c r="L71" s="60"/>
-      <c r="M71" s="60"/>
-      <c r="N71" s="60"/>
-      <c r="O71" s="60"/>
-      <c r="P71" s="60"/>
-      <c r="Q71" s="60"/>
-    </row>
-    <row r="72" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I71" s="45"/>
+      <c r="J71" s="45"/>
+      <c r="K71" s="46"/>
+      <c r="L71" s="46"/>
+      <c r="M71" s="46"/>
+      <c r="N71" s="46"/>
+      <c r="O71" s="46"/>
+      <c r="P71" s="46"/>
+      <c r="Q71" s="46"/>
+    </row>
+    <row r="72" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -4759,18 +4745,18 @@
       <c r="E72" s="17"/>
       <c r="F72" s="17"/>
       <c r="G72" s="17"/>
-      <c r="H72" s="28"/>
-      <c r="I72" s="28"/>
-      <c r="J72" s="28"/>
-      <c r="K72" s="29"/>
-      <c r="L72" s="29"/>
-      <c r="M72" s="29"/>
-      <c r="N72" s="29"/>
-      <c r="O72" s="29"/>
-      <c r="P72" s="29"/>
-      <c r="Q72" s="29"/>
-    </row>
-    <row r="73" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="28"/>
+      <c r="L72" s="28"/>
+      <c r="M72" s="28"/>
+      <c r="N72" s="28"/>
+      <c r="O72" s="28"/>
+      <c r="P72" s="28"/>
+      <c r="Q72" s="28"/>
+    </row>
+    <row r="73" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A73" s="17"/>
       <c r="B73" s="18" t="s">
         <v>17</v>
@@ -4791,7 +4777,7 @@
       <c r="P73" s="17"/>
       <c r="Q73" s="17"/>
     </row>
-    <row r="74" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A74" s="17"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -4799,24 +4785,24 @@
       <c r="E74" s="17"/>
       <c r="F74" s="17"/>
       <c r="G74" s="17"/>
-      <c r="H74" s="74"/>
-      <c r="I74" s="74"/>
-      <c r="J74" s="74"/>
+      <c r="H74" s="83"/>
+      <c r="I74" s="83"/>
+      <c r="J74" s="83"/>
       <c r="K74" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="L74" s="75"/>
-      <c r="M74" s="75"/>
+      <c r="L74" s="84"/>
+      <c r="M74" s="84"/>
       <c r="N74" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="O74" s="75"/>
-      <c r="P74" s="75"/>
+      <c r="O74" s="84"/>
+      <c r="P74" s="84"/>
       <c r="Q74" s="25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A75" s="17"/>
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
@@ -4837,7 +4823,7 @@
       <c r="P75" s="17"/>
       <c r="Q75" s="17"/>
     </row>
-    <row r="76" spans="1:19" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:19" ht="6.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A76" s="17"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -4856,7 +4842,7 @@
       <c r="P76" s="17"/>
       <c r="Q76" s="17"/>
     </row>
-    <row r="77" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A77" s="17"/>
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
@@ -4864,20 +4850,20 @@
       <c r="E77" s="17"/>
       <c r="F77" s="17"/>
       <c r="G77" s="17"/>
-      <c r="H77" s="61" t="s">
+      <c r="H77" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="I77" s="61"/>
-      <c r="J77" s="61"/>
-      <c r="K77" s="56"/>
-      <c r="L77" s="56"/>
-      <c r="M77" s="56"/>
-      <c r="N77" s="56"/>
-      <c r="O77" s="56"/>
-      <c r="P77" s="56"/>
-      <c r="Q77" s="56"/>
-    </row>
-    <row r="78" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I77" s="100"/>
+      <c r="J77" s="100"/>
+      <c r="K77" s="97"/>
+      <c r="L77" s="97"/>
+      <c r="M77" s="97"/>
+      <c r="N77" s="97"/>
+      <c r="O77" s="97"/>
+      <c r="P77" s="97"/>
+      <c r="Q77" s="97"/>
+    </row>
+    <row r="78" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A78" s="17"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -4885,20 +4871,20 @@
       <c r="E78" s="17"/>
       <c r="F78" s="17"/>
       <c r="G78" s="17"/>
-      <c r="H78" s="61" t="s">
+      <c r="H78" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="I78" s="61"/>
-      <c r="J78" s="61"/>
-      <c r="K78" s="56"/>
-      <c r="L78" s="56"/>
-      <c r="M78" s="56"/>
-      <c r="N78" s="56"/>
-      <c r="O78" s="56"/>
-      <c r="P78" s="56"/>
-      <c r="Q78" s="56"/>
-    </row>
-    <row r="79" spans="1:19" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I78" s="100"/>
+      <c r="J78" s="100"/>
+      <c r="K78" s="97"/>
+      <c r="L78" s="97"/>
+      <c r="M78" s="97"/>
+      <c r="N78" s="97"/>
+      <c r="O78" s="97"/>
+      <c r="P78" s="97"/>
+      <c r="Q78" s="97"/>
+    </row>
+    <row r="79" spans="1:19" ht="4.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A79" s="17"/>
       <c r="B79" s="17"/>
       <c r="C79" s="17"/>
@@ -4917,7 +4903,7 @@
       <c r="P79" s="17"/>
       <c r="Q79" s="17"/>
     </row>
-    <row r="80" spans="1:19" s="4" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:19" s="4" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A80" s="11"/>
       <c r="B80" s="11"/>
       <c r="C80" s="11"/>
@@ -4936,8 +4922,8 @@
       <c r="P80" s="11"/>
       <c r="Q80" s="11"/>
     </row>
-    <row r="81" spans="1:17" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="39" t="s">
+    <row r="81" spans="1:17" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A81" s="37" t="s">
         <v>42</v>
       </c>
       <c r="B81" s="11"/>
@@ -4957,7 +4943,7 @@
       <c r="P81" s="11"/>
       <c r="Q81" s="11"/>
     </row>
-    <row r="82" spans="1:17" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A82" s="19" t="s">
         <v>23</v>
       </c>
@@ -4978,7 +4964,7 @@
       <c r="P82" s="11"/>
       <c r="Q82" s="11"/>
     </row>
-    <row r="83" spans="1:17" s="4" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" s="4" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A83" s="19"/>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
@@ -4997,89 +4983,89 @@
       <c r="P83" s="11"/>
       <c r="Q83" s="11"/>
     </row>
-    <row r="84" spans="1:17" s="4" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" s="4" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A84" s="20">
         <v>1</v>
       </c>
-      <c r="B84" s="57" t="s">
+      <c r="B84" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="C84" s="57"/>
-      <c r="D84" s="57"/>
-      <c r="E84" s="57"/>
-      <c r="F84" s="57"/>
-      <c r="G84" s="57"/>
-      <c r="H84" s="57"/>
-      <c r="I84" s="57"/>
-      <c r="J84" s="57"/>
-      <c r="K84" s="57"/>
-      <c r="L84" s="57"/>
-      <c r="M84" s="57"/>
-      <c r="N84" s="57"/>
-      <c r="O84" s="57"/>
-      <c r="P84" s="57"/>
-      <c r="Q84" s="57"/>
-    </row>
-    <row r="85" spans="1:17" s="4" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C84" s="55"/>
+      <c r="D84" s="55"/>
+      <c r="E84" s="55"/>
+      <c r="F84" s="55"/>
+      <c r="G84" s="55"/>
+      <c r="H84" s="55"/>
+      <c r="I84" s="55"/>
+      <c r="J84" s="55"/>
+      <c r="K84" s="55"/>
+      <c r="L84" s="55"/>
+      <c r="M84" s="55"/>
+      <c r="N84" s="55"/>
+      <c r="O84" s="55"/>
+      <c r="P84" s="55"/>
+      <c r="Q84" s="55"/>
+    </row>
+    <row r="85" spans="1:17" s="4" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A85" s="21"/>
-      <c r="B85" s="106" t="s">
+      <c r="B85" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="107"/>
-      <c r="D85" s="107"/>
-      <c r="E85" s="107"/>
-      <c r="F85" s="107"/>
-      <c r="G85" s="107"/>
-      <c r="H85" s="107"/>
-      <c r="I85" s="107"/>
-      <c r="J85" s="107"/>
-      <c r="K85" s="107"/>
-      <c r="L85" s="107"/>
-      <c r="M85" s="107"/>
-      <c r="N85" s="107"/>
-      <c r="O85" s="107"/>
-      <c r="P85" s="107"/>
-      <c r="Q85" s="108"/>
-    </row>
-    <row r="86" spans="1:17" s="4" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C85" s="48"/>
+      <c r="D85" s="48"/>
+      <c r="E85" s="48"/>
+      <c r="F85" s="48"/>
+      <c r="G85" s="48"/>
+      <c r="H85" s="48"/>
+      <c r="I85" s="48"/>
+      <c r="J85" s="48"/>
+      <c r="K85" s="48"/>
+      <c r="L85" s="48"/>
+      <c r="M85" s="48"/>
+      <c r="N85" s="48"/>
+      <c r="O85" s="48"/>
+      <c r="P85" s="48"/>
+      <c r="Q85" s="49"/>
+    </row>
+    <row r="86" spans="1:17" s="4" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A86" s="3"/>
-      <c r="B86" s="109"/>
-      <c r="C86" s="105"/>
-      <c r="D86" s="105"/>
-      <c r="E86" s="105"/>
-      <c r="F86" s="105"/>
-      <c r="G86" s="105"/>
-      <c r="H86" s="105"/>
-      <c r="I86" s="105"/>
-      <c r="J86" s="105"/>
-      <c r="K86" s="105"/>
-      <c r="L86" s="105"/>
-      <c r="M86" s="105"/>
-      <c r="N86" s="105"/>
-      <c r="O86" s="105"/>
-      <c r="P86" s="105"/>
-      <c r="Q86" s="110"/>
-    </row>
-    <row r="87" spans="1:17" s="4" customFormat="1" ht="329.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B86" s="50"/>
+      <c r="C86" s="44"/>
+      <c r="D86" s="44"/>
+      <c r="E86" s="44"/>
+      <c r="F86" s="44"/>
+      <c r="G86" s="44"/>
+      <c r="H86" s="44"/>
+      <c r="I86" s="44"/>
+      <c r="J86" s="44"/>
+      <c r="K86" s="44"/>
+      <c r="L86" s="44"/>
+      <c r="M86" s="44"/>
+      <c r="N86" s="44"/>
+      <c r="O86" s="44"/>
+      <c r="P86" s="44"/>
+      <c r="Q86" s="51"/>
+    </row>
+    <row r="87" spans="1:17" s="4" customFormat="1" ht="329.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A87" s="21"/>
-      <c r="B87" s="111"/>
-      <c r="C87" s="112"/>
-      <c r="D87" s="112"/>
-      <c r="E87" s="112"/>
-      <c r="F87" s="112"/>
-      <c r="G87" s="112"/>
-      <c r="H87" s="112"/>
-      <c r="I87" s="112"/>
-      <c r="J87" s="112"/>
-      <c r="K87" s="112"/>
-      <c r="L87" s="112"/>
-      <c r="M87" s="112"/>
-      <c r="N87" s="112"/>
-      <c r="O87" s="112"/>
-      <c r="P87" s="112"/>
-      <c r="Q87" s="113"/>
-    </row>
-    <row r="88" spans="1:17" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B87" s="52"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53"/>
+      <c r="H87" s="53"/>
+      <c r="I87" s="53"/>
+      <c r="J87" s="53"/>
+      <c r="K87" s="53"/>
+      <c r="L87" s="53"/>
+      <c r="M87" s="53"/>
+      <c r="N87" s="53"/>
+      <c r="O87" s="53"/>
+      <c r="P87" s="53"/>
+      <c r="Q87" s="54"/>
+    </row>
+    <row r="88" spans="1:17" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A88" s="21"/>
       <c r="B88" s="22"/>
       <c r="C88" s="22"/>
@@ -5098,13 +5084,13 @@
       <c r="P88" s="22"/>
       <c r="Q88" s="22"/>
     </row>
-    <row r="89" spans="1:17" s="4" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="39" t="s">
+    <row r="89" spans="1:17" s="4" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A89" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B89" s="31"/>
-      <c r="C89" s="31"/>
-      <c r="D89" s="31"/>
+      <c r="B89" s="22"/>
+      <c r="C89" s="22"/>
+      <c r="D89" s="22"/>
       <c r="E89" s="22"/>
       <c r="F89" s="22"/>
       <c r="G89" s="22"/>
@@ -5119,7 +5105,7 @@
       <c r="P89" s="22"/>
       <c r="Q89" s="22"/>
     </row>
-    <row r="90" spans="1:17" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A90" s="27"/>
       <c r="B90" s="22"/>
       <c r="C90" s="22"/>
@@ -5138,99 +5124,99 @@
       <c r="P90" s="22"/>
       <c r="Q90" s="22"/>
     </row>
-    <row r="91" spans="1:17" s="4" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" s="4" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A91" s="24">
         <v>2</v>
       </c>
-      <c r="B91" s="57" t="s">
+      <c r="B91" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="C91" s="57"/>
-      <c r="D91" s="57"/>
-      <c r="E91" s="57"/>
-      <c r="F91" s="57"/>
-      <c r="G91" s="57"/>
-      <c r="H91" s="57"/>
-      <c r="I91" s="57"/>
-      <c r="J91" s="57"/>
-      <c r="K91" s="57"/>
-      <c r="L91" s="57"/>
-      <c r="M91" s="57"/>
-      <c r="N91" s="57"/>
-      <c r="O91" s="57"/>
-      <c r="P91" s="57"/>
-      <c r="Q91" s="57"/>
-    </row>
-    <row r="92" spans="1:17" s="4" customFormat="1" ht="122.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C91" s="55"/>
+      <c r="D91" s="55"/>
+      <c r="E91" s="55"/>
+      <c r="F91" s="55"/>
+      <c r="G91" s="55"/>
+      <c r="H91" s="55"/>
+      <c r="I91" s="55"/>
+      <c r="J91" s="55"/>
+      <c r="K91" s="55"/>
+      <c r="L91" s="55"/>
+      <c r="M91" s="55"/>
+      <c r="N91" s="55"/>
+      <c r="O91" s="55"/>
+      <c r="P91" s="55"/>
+      <c r="Q91" s="55"/>
+    </row>
+    <row r="92" spans="1:17" s="4" customFormat="1" ht="122.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A92" s="20">
         <v>3</v>
       </c>
-      <c r="B92" s="57" t="s">
+      <c r="B92" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="C92" s="57"/>
-      <c r="D92" s="57"/>
-      <c r="E92" s="57"/>
-      <c r="F92" s="57"/>
-      <c r="G92" s="57"/>
-      <c r="H92" s="57"/>
-      <c r="I92" s="57"/>
-      <c r="J92" s="57"/>
-      <c r="K92" s="57"/>
-      <c r="L92" s="57"/>
-      <c r="M92" s="57"/>
-      <c r="N92" s="57"/>
-      <c r="O92" s="57"/>
-      <c r="P92" s="57"/>
-      <c r="Q92" s="57"/>
-    </row>
-    <row r="93" spans="1:17" s="4" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C92" s="55"/>
+      <c r="D92" s="55"/>
+      <c r="E92" s="55"/>
+      <c r="F92" s="55"/>
+      <c r="G92" s="55"/>
+      <c r="H92" s="55"/>
+      <c r="I92" s="55"/>
+      <c r="J92" s="55"/>
+      <c r="K92" s="55"/>
+      <c r="L92" s="55"/>
+      <c r="M92" s="55"/>
+      <c r="N92" s="55"/>
+      <c r="O92" s="55"/>
+      <c r="P92" s="55"/>
+      <c r="Q92" s="55"/>
+    </row>
+    <row r="93" spans="1:17" s="4" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A93" s="20">
         <v>4</v>
       </c>
-      <c r="B93" s="57" t="s">
+      <c r="B93" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="C93" s="57"/>
-      <c r="D93" s="57"/>
-      <c r="E93" s="57"/>
-      <c r="F93" s="57"/>
-      <c r="G93" s="57"/>
-      <c r="H93" s="57"/>
-      <c r="I93" s="57"/>
-      <c r="J93" s="57"/>
-      <c r="K93" s="57"/>
-      <c r="L93" s="57"/>
-      <c r="M93" s="57"/>
-      <c r="N93" s="57"/>
-      <c r="O93" s="57"/>
-      <c r="P93" s="57"/>
-      <c r="Q93" s="57"/>
-    </row>
-    <row r="94" spans="1:17" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="45">
+      <c r="C93" s="55"/>
+      <c r="D93" s="55"/>
+      <c r="E93" s="55"/>
+      <c r="F93" s="55"/>
+      <c r="G93" s="55"/>
+      <c r="H93" s="55"/>
+      <c r="I93" s="55"/>
+      <c r="J93" s="55"/>
+      <c r="K93" s="55"/>
+      <c r="L93" s="55"/>
+      <c r="M93" s="55"/>
+      <c r="N93" s="55"/>
+      <c r="O93" s="55"/>
+      <c r="P93" s="55"/>
+      <c r="Q93" s="55"/>
+    </row>
+    <row r="94" spans="1:17" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A94" s="43">
         <v>5</v>
       </c>
-      <c r="B94" s="105" t="s">
+      <c r="B94" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="C94" s="105"/>
-      <c r="D94" s="105"/>
-      <c r="E94" s="105"/>
-      <c r="F94" s="105"/>
-      <c r="G94" s="105"/>
-      <c r="H94" s="105"/>
-      <c r="I94" s="105"/>
-      <c r="J94" s="105"/>
-      <c r="K94" s="105"/>
-      <c r="L94" s="105"/>
-      <c r="M94" s="105"/>
-      <c r="N94" s="105"/>
-      <c r="O94" s="105"/>
-      <c r="P94" s="105"/>
-      <c r="Q94" s="105"/>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="C94" s="44"/>
+      <c r="D94" s="44"/>
+      <c r="E94" s="44"/>
+      <c r="F94" s="44"/>
+      <c r="G94" s="44"/>
+      <c r="H94" s="44"/>
+      <c r="I94" s="44"/>
+      <c r="J94" s="44"/>
+      <c r="K94" s="44"/>
+      <c r="L94" s="44"/>
+      <c r="M94" s="44"/>
+      <c r="N94" s="44"/>
+      <c r="O94" s="44"/>
+      <c r="P94" s="44"/>
+      <c r="Q94" s="44"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
@@ -5249,222 +5235,264 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A96" s="42">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A96" s="40">
         <v>6</v>
       </c>
-      <c r="B96" s="105" t="s">
+      <c r="B96" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C96" s="105"/>
-      <c r="D96" s="105"/>
-      <c r="E96" s="105"/>
-      <c r="F96" s="105"/>
-      <c r="G96" s="105"/>
-      <c r="H96" s="105"/>
-      <c r="I96" s="105"/>
-      <c r="J96" s="105"/>
-      <c r="K96" s="105"/>
-      <c r="L96" s="105"/>
-      <c r="M96" s="105"/>
-      <c r="N96" s="105"/>
-      <c r="O96" s="105"/>
-      <c r="P96" s="105"/>
-      <c r="Q96" s="105"/>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A97" s="41"/>
-      <c r="B97" s="105"/>
-      <c r="C97" s="105"/>
-      <c r="D97" s="105"/>
-      <c r="E97" s="105"/>
-      <c r="F97" s="105"/>
-      <c r="G97" s="105"/>
-      <c r="H97" s="105"/>
-      <c r="I97" s="105"/>
-      <c r="J97" s="105"/>
-      <c r="K97" s="105"/>
-      <c r="L97" s="105"/>
-      <c r="M97" s="105"/>
-      <c r="N97" s="105"/>
-      <c r="O97" s="105"/>
-      <c r="P97" s="105"/>
-      <c r="Q97" s="105"/>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A98" s="41"/>
-      <c r="B98" s="105"/>
-      <c r="C98" s="105"/>
-      <c r="D98" s="105"/>
-      <c r="E98" s="105"/>
-      <c r="F98" s="105"/>
-      <c r="G98" s="105"/>
-      <c r="H98" s="105"/>
-      <c r="I98" s="105"/>
-      <c r="J98" s="105"/>
-      <c r="K98" s="105"/>
-      <c r="L98" s="105"/>
-      <c r="M98" s="105"/>
-      <c r="N98" s="105"/>
-      <c r="O98" s="105"/>
-      <c r="P98" s="105"/>
-      <c r="Q98" s="105"/>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A99" s="41"/>
-      <c r="B99" s="105"/>
-      <c r="C99" s="105"/>
-      <c r="D99" s="105"/>
-      <c r="E99" s="105"/>
-      <c r="F99" s="105"/>
-      <c r="G99" s="105"/>
-      <c r="H99" s="105"/>
-      <c r="I99" s="105"/>
-      <c r="J99" s="105"/>
-      <c r="K99" s="105"/>
-      <c r="L99" s="105"/>
-      <c r="M99" s="105"/>
-      <c r="N99" s="105"/>
-      <c r="O99" s="105"/>
-      <c r="P99" s="105"/>
-      <c r="Q99" s="105"/>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A100" s="41"/>
-      <c r="B100" s="105"/>
-      <c r="C100" s="105"/>
-      <c r="D100" s="105"/>
-      <c r="E100" s="105"/>
-      <c r="F100" s="105"/>
-      <c r="G100" s="105"/>
-      <c r="H100" s="105"/>
-      <c r="I100" s="105"/>
-      <c r="J100" s="105"/>
-      <c r="K100" s="105"/>
-      <c r="L100" s="105"/>
-      <c r="M100" s="105"/>
-      <c r="N100" s="105"/>
-      <c r="O100" s="105"/>
-      <c r="P100" s="105"/>
-      <c r="Q100" s="105"/>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A101" s="41"/>
-      <c r="B101" s="105"/>
-      <c r="C101" s="105"/>
-      <c r="D101" s="105"/>
-      <c r="E101" s="105"/>
-      <c r="F101" s="105"/>
-      <c r="G101" s="105"/>
-      <c r="H101" s="105"/>
-      <c r="I101" s="105"/>
-      <c r="J101" s="105"/>
-      <c r="K101" s="105"/>
-      <c r="L101" s="105"/>
-      <c r="M101" s="105"/>
-      <c r="N101" s="105"/>
-      <c r="O101" s="105"/>
-      <c r="P101" s="105"/>
-      <c r="Q101" s="105"/>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A102" s="41"/>
-      <c r="B102" s="105"/>
-      <c r="C102" s="105"/>
-      <c r="D102" s="105"/>
-      <c r="E102" s="105"/>
-      <c r="F102" s="105"/>
-      <c r="G102" s="105"/>
-      <c r="H102" s="105"/>
-      <c r="I102" s="105"/>
-      <c r="J102" s="105"/>
-      <c r="K102" s="105"/>
-      <c r="L102" s="105"/>
-      <c r="M102" s="105"/>
-      <c r="N102" s="105"/>
-      <c r="O102" s="105"/>
-      <c r="P102" s="105"/>
-      <c r="Q102" s="105"/>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A103" s="41"/>
-      <c r="B103" s="105"/>
-      <c r="C103" s="105"/>
-      <c r="D103" s="105"/>
-      <c r="E103" s="105"/>
-      <c r="F103" s="105"/>
-      <c r="G103" s="105"/>
-      <c r="H103" s="105"/>
-      <c r="I103" s="105"/>
-      <c r="J103" s="105"/>
-      <c r="K103" s="105"/>
-      <c r="L103" s="105"/>
-      <c r="M103" s="105"/>
-      <c r="N103" s="105"/>
-      <c r="O103" s="105"/>
-      <c r="P103" s="105"/>
-      <c r="Q103" s="105"/>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A104" s="41"/>
-      <c r="B104" s="105"/>
-      <c r="C104" s="105"/>
-      <c r="D104" s="105"/>
-      <c r="E104" s="105"/>
-      <c r="F104" s="105"/>
-      <c r="G104" s="105"/>
-      <c r="H104" s="105"/>
-      <c r="I104" s="105"/>
-      <c r="J104" s="105"/>
-      <c r="K104" s="105"/>
-      <c r="L104" s="105"/>
-      <c r="M104" s="105"/>
-      <c r="N104" s="105"/>
-      <c r="O104" s="105"/>
-      <c r="P104" s="105"/>
-      <c r="Q104" s="105"/>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A105" s="41"/>
-      <c r="B105" s="105"/>
-      <c r="C105" s="105"/>
-      <c r="D105" s="105"/>
-      <c r="E105" s="105"/>
-      <c r="F105" s="105"/>
-      <c r="G105" s="105"/>
-      <c r="H105" s="105"/>
-      <c r="I105" s="105"/>
-      <c r="J105" s="105"/>
-      <c r="K105" s="105"/>
-      <c r="L105" s="105"/>
-      <c r="M105" s="105"/>
-      <c r="N105" s="105"/>
-      <c r="O105" s="105"/>
-      <c r="P105" s="105"/>
-      <c r="Q105" s="105"/>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A106" s="41"/>
-      <c r="B106" s="105"/>
-      <c r="C106" s="105"/>
-      <c r="D106" s="105"/>
-      <c r="E106" s="105"/>
-      <c r="F106" s="105"/>
-      <c r="G106" s="105"/>
-      <c r="H106" s="105"/>
-      <c r="I106" s="105"/>
-      <c r="J106" s="105"/>
-      <c r="K106" s="105"/>
-      <c r="L106" s="105"/>
-      <c r="M106" s="105"/>
-      <c r="N106" s="105"/>
-      <c r="O106" s="105"/>
-      <c r="P106" s="105"/>
-      <c r="Q106" s="105"/>
+      <c r="C96" s="44"/>
+      <c r="D96" s="44"/>
+      <c r="E96" s="44"/>
+      <c r="F96" s="44"/>
+      <c r="G96" s="44"/>
+      <c r="H96" s="44"/>
+      <c r="I96" s="44"/>
+      <c r="J96" s="44"/>
+      <c r="K96" s="44"/>
+      <c r="L96" s="44"/>
+      <c r="M96" s="44"/>
+      <c r="N96" s="44"/>
+      <c r="O96" s="44"/>
+      <c r="P96" s="44"/>
+      <c r="Q96" s="44"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A97" s="39"/>
+      <c r="B97" s="44"/>
+      <c r="C97" s="44"/>
+      <c r="D97" s="44"/>
+      <c r="E97" s="44"/>
+      <c r="F97" s="44"/>
+      <c r="G97" s="44"/>
+      <c r="H97" s="44"/>
+      <c r="I97" s="44"/>
+      <c r="J97" s="44"/>
+      <c r="K97" s="44"/>
+      <c r="L97" s="44"/>
+      <c r="M97" s="44"/>
+      <c r="N97" s="44"/>
+      <c r="O97" s="44"/>
+      <c r="P97" s="44"/>
+      <c r="Q97" s="44"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A98" s="39"/>
+      <c r="B98" s="44"/>
+      <c r="C98" s="44"/>
+      <c r="D98" s="44"/>
+      <c r="E98" s="44"/>
+      <c r="F98" s="44"/>
+      <c r="G98" s="44"/>
+      <c r="H98" s="44"/>
+      <c r="I98" s="44"/>
+      <c r="J98" s="44"/>
+      <c r="K98" s="44"/>
+      <c r="L98" s="44"/>
+      <c r="M98" s="44"/>
+      <c r="N98" s="44"/>
+      <c r="O98" s="44"/>
+      <c r="P98" s="44"/>
+      <c r="Q98" s="44"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A99" s="39"/>
+      <c r="B99" s="44"/>
+      <c r="C99" s="44"/>
+      <c r="D99" s="44"/>
+      <c r="E99" s="44"/>
+      <c r="F99" s="44"/>
+      <c r="G99" s="44"/>
+      <c r="H99" s="44"/>
+      <c r="I99" s="44"/>
+      <c r="J99" s="44"/>
+      <c r="K99" s="44"/>
+      <c r="L99" s="44"/>
+      <c r="M99" s="44"/>
+      <c r="N99" s="44"/>
+      <c r="O99" s="44"/>
+      <c r="P99" s="44"/>
+      <c r="Q99" s="44"/>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A100" s="39"/>
+      <c r="B100" s="44"/>
+      <c r="C100" s="44"/>
+      <c r="D100" s="44"/>
+      <c r="E100" s="44"/>
+      <c r="F100" s="44"/>
+      <c r="G100" s="44"/>
+      <c r="H100" s="44"/>
+      <c r="I100" s="44"/>
+      <c r="J100" s="44"/>
+      <c r="K100" s="44"/>
+      <c r="L100" s="44"/>
+      <c r="M100" s="44"/>
+      <c r="N100" s="44"/>
+      <c r="O100" s="44"/>
+      <c r="P100" s="44"/>
+      <c r="Q100" s="44"/>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A101" s="39"/>
+      <c r="B101" s="44"/>
+      <c r="C101" s="44"/>
+      <c r="D101" s="44"/>
+      <c r="E101" s="44"/>
+      <c r="F101" s="44"/>
+      <c r="G101" s="44"/>
+      <c r="H101" s="44"/>
+      <c r="I101" s="44"/>
+      <c r="J101" s="44"/>
+      <c r="K101" s="44"/>
+      <c r="L101" s="44"/>
+      <c r="M101" s="44"/>
+      <c r="N101" s="44"/>
+      <c r="O101" s="44"/>
+      <c r="P101" s="44"/>
+      <c r="Q101" s="44"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A102" s="39"/>
+      <c r="B102" s="44"/>
+      <c r="C102" s="44"/>
+      <c r="D102" s="44"/>
+      <c r="E102" s="44"/>
+      <c r="F102" s="44"/>
+      <c r="G102" s="44"/>
+      <c r="H102" s="44"/>
+      <c r="I102" s="44"/>
+      <c r="J102" s="44"/>
+      <c r="K102" s="44"/>
+      <c r="L102" s="44"/>
+      <c r="M102" s="44"/>
+      <c r="N102" s="44"/>
+      <c r="O102" s="44"/>
+      <c r="P102" s="44"/>
+      <c r="Q102" s="44"/>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A103" s="39"/>
+      <c r="B103" s="44"/>
+      <c r="C103" s="44"/>
+      <c r="D103" s="44"/>
+      <c r="E103" s="44"/>
+      <c r="F103" s="44"/>
+      <c r="G103" s="44"/>
+      <c r="H103" s="44"/>
+      <c r="I103" s="44"/>
+      <c r="J103" s="44"/>
+      <c r="K103" s="44"/>
+      <c r="L103" s="44"/>
+      <c r="M103" s="44"/>
+      <c r="N103" s="44"/>
+      <c r="O103" s="44"/>
+      <c r="P103" s="44"/>
+      <c r="Q103" s="44"/>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A104" s="39"/>
+      <c r="B104" s="44"/>
+      <c r="C104" s="44"/>
+      <c r="D104" s="44"/>
+      <c r="E104" s="44"/>
+      <c r="F104" s="44"/>
+      <c r="G104" s="44"/>
+      <c r="H104" s="44"/>
+      <c r="I104" s="44"/>
+      <c r="J104" s="44"/>
+      <c r="K104" s="44"/>
+      <c r="L104" s="44"/>
+      <c r="M104" s="44"/>
+      <c r="N104" s="44"/>
+      <c r="O104" s="44"/>
+      <c r="P104" s="44"/>
+      <c r="Q104" s="44"/>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A105" s="39"/>
+      <c r="B105" s="44"/>
+      <c r="C105" s="44"/>
+      <c r="D105" s="44"/>
+      <c r="E105" s="44"/>
+      <c r="F105" s="44"/>
+      <c r="G105" s="44"/>
+      <c r="H105" s="44"/>
+      <c r="I105" s="44"/>
+      <c r="J105" s="44"/>
+      <c r="K105" s="44"/>
+      <c r="L105" s="44"/>
+      <c r="M105" s="44"/>
+      <c r="N105" s="44"/>
+      <c r="O105" s="44"/>
+      <c r="P105" s="44"/>
+      <c r="Q105" s="44"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A106" s="39"/>
+      <c r="B106" s="44"/>
+      <c r="C106" s="44"/>
+      <c r="D106" s="44"/>
+      <c r="E106" s="44"/>
+      <c r="F106" s="44"/>
+      <c r="G106" s="44"/>
+      <c r="H106" s="44"/>
+      <c r="I106" s="44"/>
+      <c r="J106" s="44"/>
+      <c r="K106" s="44"/>
+      <c r="L106" s="44"/>
+      <c r="M106" s="44"/>
+      <c r="N106" s="44"/>
+      <c r="O106" s="44"/>
+      <c r="P106" s="44"/>
+      <c r="Q106" s="44"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="0m8dFwNOBjxPDOZxYrRnbykw+pURR2J+eXyiVyzAv/CrptkO8RpEjhrW4KDuresIJoCPDn5hR08jQkNGJWm24Q==" saltValue="cTHfXTr8FLbhqiJLF5H8Fw==" spinCount="100000" sheet="1" scenarios="1"/>
   <mergeCells count="58">
+    <mergeCell ref="P48:Q50"/>
+    <mergeCell ref="B48:O50"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="F53:Q53"/>
+    <mergeCell ref="K77:Q77"/>
+    <mergeCell ref="B84:Q84"/>
+    <mergeCell ref="F54:Q58"/>
+    <mergeCell ref="A54:E58"/>
+    <mergeCell ref="H64:J64"/>
+    <mergeCell ref="K64:Q64"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="K78:Q78"/>
+    <mergeCell ref="A19:Q24"/>
+    <mergeCell ref="B14:Q14"/>
+    <mergeCell ref="B93:Q93"/>
+    <mergeCell ref="B28:Q28"/>
+    <mergeCell ref="A29:Q34"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="O74:P74"/>
+    <mergeCell ref="B39:Q39"/>
+    <mergeCell ref="A40:Q47"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="K67:Q67"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="B18:Q18"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="B6:Q6"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A7:O7"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="P9:Q9"/>
     <mergeCell ref="B96:Q106"/>
     <mergeCell ref="H65:J65"/>
     <mergeCell ref="K65:Q65"/>
@@ -5481,48 +5509,6 @@
     <mergeCell ref="B85:Q87"/>
     <mergeCell ref="B91:Q91"/>
     <mergeCell ref="B92:Q92"/>
-    <mergeCell ref="B18:Q18"/>
-    <mergeCell ref="A3:Q3"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="B6:Q6"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A7:O7"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="A9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="A19:Q24"/>
-    <mergeCell ref="B14:Q14"/>
-    <mergeCell ref="B93:Q93"/>
-    <mergeCell ref="B28:Q28"/>
-    <mergeCell ref="A29:Q34"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="O74:P74"/>
-    <mergeCell ref="B39:Q39"/>
-    <mergeCell ref="A40:Q47"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="O61:P61"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="K67:Q67"/>
-    <mergeCell ref="H68:J68"/>
-    <mergeCell ref="K77:Q77"/>
-    <mergeCell ref="B84:Q84"/>
-    <mergeCell ref="F54:Q58"/>
-    <mergeCell ref="A54:E58"/>
-    <mergeCell ref="H64:J64"/>
-    <mergeCell ref="K64:Q64"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="H78:J78"/>
-    <mergeCell ref="K78:Q78"/>
-    <mergeCell ref="P48:Q50"/>
-    <mergeCell ref="B48:O50"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="F53:Q53"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -5633,12 +5619,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
+    <Owner xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5863,27 +5858,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
-    <Owner xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08C3EFCC-5A57-4E10-BDF2-53F8589720A7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0825739-CC56-45B4-9488-5ABEA9CCB284}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="2bc05441-ecb8-41d0-9872-2862fef3ebb0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5908,18 +5903,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0825739-CC56-45B4-9488-5ABEA9CCB284}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08C3EFCC-5A57-4E10-BDF2-53F8589720A7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="2bc05441-ecb8-41d0-9872-2862fef3ebb0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>